--- a/output/Data and Chart Outputs/china_nbs_retail_sales_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_retail_sales_monthly.xlsx
@@ -159,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China retail sales y/y total (NBS) (to Aug/26)</a:t>
+              <a:t>China retail sales y/y total (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -195,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$131</f>
+              <f>'Chart'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$131</f>
+              <f>'Chart'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -231,12 +231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$131</f>
+              <f>'Chart'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$131</f>
+              <f>'Chart'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -267,12 +267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$131</f>
+              <f>'Chart'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$131</f>
+              <f>'Chart'!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -303,12 +303,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$131</f>
+              <f>'Chart'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$131</f>
+              <f>'Chart'!$E$2:$E$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,7 +408,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China retail sales y/y selected goods (NBS) (to Aug/26)</a:t>
+              <a:t>China retail sales y/y selected goods (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$A$2:$A$90</f>
+              <f>'Chart - retail sales y-y select'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$B$2:$B$90</f>
+              <f>'Chart - retail sales y-y select'!$B$2:$B$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -480,12 +480,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$A$2:$A$90</f>
+              <f>'Chart - retail sales y-y select'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$C$2:$C$90</f>
+              <f>'Chart - retail sales y-y select'!$C$2:$C$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -516,12 +516,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$A$2:$A$90</f>
+              <f>'Chart - retail sales y-y select'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$D$2:$D$90</f>
+              <f>'Chart - retail sales y-y select'!$D$2:$D$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$A$2:$A$90</f>
+              <f>'Chart - retail sales y-y select'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - retail sales y-y select'!$E$2:$E$90</f>
+              <f>'Chart - retail sales y-y select'!$E$2:$E$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3122,6 +3122,23 @@
       </c>
       <c r="E131" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3136,7 +3153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4680,6 +4697,23 @@
       </c>
       <c r="E90" t="n">
         <v>-11.8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4694,7 +4728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA131"/>
+  <dimension ref="A1:DA132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37150,6 +37184,317 @@
       </c>
       <c r="DA131" t="n">
         <v>-9.800000000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>4243.3</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>37000.1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3879.2</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H132" t="n">
+        <v>34057.4</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1687.3</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L132" t="n">
+        <v>14038.7</v>
+      </c>
+      <c r="M132" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="P132" t="n">
+        <v>9506</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R132" t="n">
+        <v>3607.7</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T132" t="n">
+        <v>31982</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V132" t="n">
+        <v>635.6</v>
+      </c>
+      <c r="W132" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X132" t="n">
+        <v>5018.1</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>460.3</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>4196.9</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>1252.8</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>3783</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>32803.2</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1546</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>12785.9</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>1773.8</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>244.4</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>1082.4</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>39</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>349.1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>262</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>644.7</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>810.5</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>541</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>-3</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>812.3</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>1587.8</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>364.1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>2942.7</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>-9.699999999999999</v>
       </c>
     </row>
   </sheetData>
